--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92563351169</v>
+        <v>46157.93075108771</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93075108771</v>
+        <v>46157.93158004108</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93158004108</v>
+        <v>46157.93395040391</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93395040391</v>
+        <v>46157.93711671655</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93711671655</v>
+        <v>46158.28211907186</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28211907186</v>
+        <v>46158.29672905972</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29672905972</v>
+        <v>46158.29807899916</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29807899916</v>
+        <v>46158.33382701789</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33382701789</v>
+        <v>46158.36850328734</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36850328734</v>
+        <v>46158.37282820813</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
